--- a/docs/培训/OpenWorker培训/03-设备点检/维修记录.xlsx
+++ b/docs/培训/OpenWorker培训/03-设备点检/维修记录.xlsx
@@ -482,7 +482,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46260</v>
+        <v>46266</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46290</v>
+        <v>46296</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
